--- a/business_forms/023_farm_facility_inspection_form--business_forms.xlsx
+++ b/business_forms/023_farm_facility_inspection_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'large_farm',_'value':_'large_farm'}</t>
+          <t>large_farm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Large Farm', 'value': 'large_farm'}</t>
+          <t>Large Farm</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'small_farm',_'value':_'small_farm'}</t>
+          <t>small_farm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Small Farm', 'value': 'small_farm'}</t>
+          <t>Small Farm</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'livestock_farm',_'value':_'livestock_farm'}</t>
+          <t>livestock_farm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Livestock Farm', 'value': 'livestock_farm'}</t>
+          <t>Livestock Farm</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other_(please_specify)',_'value':_'other'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Other (please specify)', 'value': 'other'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'under_renovation',_'value':_'under_renovation'}</t>
+          <t>under_renovation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Under Renovation', 'value': 'under_renovation'}</t>
+          <t>Under Renovation</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Closed', 'value': 'closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jane_doe',_'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jane Doe', 'value': 'jane_doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'john_doe',_'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'John Doe', 'value': 'john_doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
